--- a/templates/ADJ_template.xlsx
+++ b/templates/ADJ_template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E1146F-A297-45F2-8346-5E1E237072E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{B8A03601-A93F-4B4E-AC05-D5A059051D62}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="0" activeTab="0" xr2:uid="{B8A03601-A93F-4B4E-AC05-D5A059051D62}"/>
   </bookViews>
   <sheets>
     <sheet name="adjust_qty_form1" sheetId="1" r:id="rId2"/>
